--- a/Data/Excel/BBString.xlsx
+++ b/Data/Excel/BBString.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\ProjectBB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3819BC06-3971-4108-8E13-F84505DB97E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA72D72E-68F1-4A30-9AC8-A7DB5E88692B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4764" yWindow="4080" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{6662192A-0435-4A7D-B3AF-CF3D1E1A9D2B}"/>
+    <workbookView xWindow="5112" yWindow="4428" windowWidth="23040" windowHeight="12120" activeTab="2" xr2:uid="{6662192A-0435-4A7D-B3AF-CF3D1E1A9D2B}"/>
   </bookViews>
   <sheets>
     <sheet name="String_Recipe" sheetId="1" r:id="rId1"/>
     <sheet name="String_Item" sheetId="2" r:id="rId2"/>
+    <sheet name="String_UI" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="235">
   <si>
     <t>body</t>
   </si>
@@ -714,14 +715,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>STR_Item_Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>테스트용</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -738,6 +731,14 @@
   </si>
   <si>
     <t>이것은 신선한 우유의 설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STR_UI_Confirm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>확인</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1194,7 +1195,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2233,13 +2234,13 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="38.296875" customWidth="1"/>
-    <col min="2" max="2" width="20.8984375" customWidth="1"/>
+    <col min="1" max="1" width="18.296875" customWidth="1"/>
+    <col min="2" max="2" width="24.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2261,20 +2262,65 @@
     </row>
     <row r="3" spans="1:3" ht="18" thickBot="1">
       <c r="A3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" t="s">
         <v>228</v>
-      </c>
-      <c r="B3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C3" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" thickBot="1">
       <c r="A4" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC2A93AF-3914-4AB0-9480-2EBFFA05F0EA}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="1" max="1" width="18.296875" customWidth="1"/>
+    <col min="2" max="2" width="24.8984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" thickBot="1">
+      <c r="A1" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1">
+      <c r="A2" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>233</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B3" t="s">
         <v>234</v>
       </c>
     </row>
